--- a/Python/results/metrics_diff.xlsx
+++ b/Python/results/metrics_diff.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28830"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22EA398F-1925-42D5-BD08-9918AB722343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3D183E8-F403-47EE-B383-8CA76F9DC8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="97">
   <si>
     <t>Pattern</t>
   </si>
@@ -63,9 +63,6 @@
     <t>requestRate_RPS</t>
   </si>
   <si>
-    <t>averageLatency</t>
-  </si>
-  <si>
     <t>95PercentileLatency</t>
   </si>
   <si>
@@ -259,6 +256,51 @@
   </si>
   <si>
     <t>0.00485583224115334</t>
+  </si>
+  <si>
+    <t>2025-05-06 12:03:28</t>
+  </si>
+  <si>
+    <t>93.30994444444444</t>
+  </si>
+  <si>
+    <t>3409903794.825926</t>
+  </si>
+  <si>
+    <t>19261382171.396297</t>
+  </si>
+  <si>
+    <t>13808119837.292593</t>
+  </si>
+  <si>
+    <t>0.0026206368474576257</t>
+  </si>
+  <si>
+    <t>0.008241379310344831</t>
+  </si>
+  <si>
+    <t>2025-05-06 12:22:01</t>
+  </si>
+  <si>
+    <t>95.03634444444444</t>
+  </si>
+  <si>
+    <t>3300299622.1370373</t>
+  </si>
+  <si>
+    <t>19595883446.155556</t>
+  </si>
+  <si>
+    <t>12988774710.981482</t>
+  </si>
+  <si>
+    <t>0.0026387976833333335</t>
+  </si>
+  <si>
+    <t>5.379495844684299</t>
+  </si>
+  <si>
+    <t>0.008541666666666663</t>
   </si>
   <si>
     <t>2025-04-22 14:48:50</t>
@@ -330,13 +372,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
@@ -664,10 +707,10 @@
     <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -701,248 +744,227 @@
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" t="s">
         <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
       </c>
       <c r="K6" t="s">
         <v>55</v>
       </c>
-      <c r="L6" t="s">
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="J7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D8" s="2">
         <v>45782.49527777778</v>
@@ -966,21 +988,18 @@
         <v>5.3791248577635198</v>
       </c>
       <c r="K8" s="1">
-        <v>3.5937797461538402E-3</v>
-      </c>
-      <c r="L8" s="1">
         <v>9.0046296296296298E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2">
         <v>45782.504155092596</v>
@@ -1004,21 +1023,18 @@
         <v>4.9655001189650996</v>
       </c>
       <c r="K9" s="1">
-        <v>2.1368593152777701E-3</v>
-      </c>
-      <c r="L9" s="1">
         <v>6.5277777777777799E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2">
         <v>45782.511157407411</v>
@@ -1042,21 +1058,18 @@
         <v>4.7172739122338703</v>
       </c>
       <c r="K10" s="1">
-        <v>2.5754683574561502E-3</v>
-      </c>
-      <c r="L10" s="1">
         <v>8.81395348837208E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
         <v>45781.659456018519</v>
@@ -1080,21 +1093,18 @@
         <v>5.3793103448275801</v>
       </c>
       <c r="K11" s="1">
-        <v>1.3895394544871801E-3</v>
-      </c>
-      <c r="L11" s="1">
         <v>4.7899159663865503E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:12">
       <c r="A12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2">
         <v>45772.332245370373</v>
@@ -1118,21 +1128,18 @@
         <v>4.9655172413793096</v>
       </c>
       <c r="K12" s="1">
-        <v>2.5613114597222101E-3</v>
-      </c>
-      <c r="L12" s="1">
         <v>7.6960784313725404E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4">
         <v>45781.673206018517</v>
@@ -1156,21 +1163,18 @@
         <v>5.3793103448275801</v>
       </c>
       <c r="K13" s="3">
-        <v>2.4240987307692198E-3</v>
-      </c>
-      <c r="L13" s="3">
         <v>8.2608695652173995E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:12">
       <c r="A14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D14" s="2">
         <v>45782.451689814814</v>
@@ -1194,21 +1198,18 @@
         <v>5.0482758620689596</v>
       </c>
       <c r="K14" s="1">
-        <v>2.2717723681693999E-3</v>
-      </c>
-      <c r="L14" s="1">
         <v>4.9144876325088304E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="2">
         <v>45782.459039351852</v>
@@ -1232,21 +1233,18 @@
         <v>5.3711425039853102</v>
       </c>
       <c r="K15" s="1">
-        <v>3.2678692512820499E-3</v>
-      </c>
-      <c r="L15" s="1">
         <v>9.6551724137930901E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2">
         <v>45782.46702546296</v>
@@ -1270,21 +1268,18 @@
         <v>5.13085755663597</v>
       </c>
       <c r="K16" s="1">
-        <v>4.9493327775537504E-3</v>
-      </c>
-      <c r="L16" s="1">
         <v>1.9439024390243899E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2">
         <v>45771.932604166665</v>
@@ -1308,21 +1303,18 @@
         <v>5.3793103448275801</v>
       </c>
       <c r="K17" s="1">
-        <v>1.8778488923076901E-3</v>
-      </c>
-      <c r="L17" s="1">
         <v>4.8242187500000004E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2">
         <v>45771.943854166668</v>
@@ -1346,21 +1338,18 @@
         <v>5.2965334602294396</v>
       </c>
       <c r="K18" s="1">
-        <v>1.8995031914062399E-3</v>
-      </c>
-      <c r="L18" s="1">
         <v>5.7076923076922904E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:11">
       <c r="A19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="4">
         <v>45771.951041666667</v>
@@ -1384,21 +1373,18 @@
         <v>4.5482758620689596</v>
       </c>
       <c r="K19" s="3">
-        <v>2.4634577172100002E-3</v>
-      </c>
-      <c r="L19" s="3">
         <v>8.4960317460317392E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D20" s="2">
         <v>45772.48097222222</v>
@@ -1422,21 +1408,18 @@
         <v>5.3793103448275801</v>
       </c>
       <c r="K20" s="1">
-        <v>1.7866882807692299E-3</v>
-      </c>
-      <c r="L20" s="1">
         <v>4.8085658663205699E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="2">
         <v>45781.917326388888</v>
@@ -1460,21 +1443,18 @@
         <v>5.3793845432350702</v>
       </c>
       <c r="K21" s="1">
-        <v>2.7904682089743399E-3</v>
-      </c>
-      <c r="L21" s="1">
         <v>8.4589041095890303E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" s="2">
         <v>45781.92591435185</v>
@@ -1498,21 +1478,18 @@
         <v>5.3793103448275801</v>
       </c>
       <c r="K22" s="1">
-        <v>2.8793402608973898E-3</v>
-      </c>
-      <c r="L22" s="1">
         <v>8.9361702127659596E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2">
         <v>45771.896435185183</v>
@@ -1536,21 +1513,18 @@
         <v>5.3792917955455302</v>
       </c>
       <c r="K23" s="1">
-        <v>2.3162680089743501E-3</v>
-      </c>
-      <c r="L23" s="1">
         <v>4.8085658663205699E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="2">
         <v>45771.904548611114</v>
@@ -1574,21 +1548,18 @@
         <v>5.3793288942375597</v>
       </c>
       <c r="K24" s="1">
-        <v>5.2775129967948496E-3</v>
-      </c>
-      <c r="L24" s="1">
         <v>2.1612903225806401E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:11">
       <c r="A25" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" s="4">
         <v>45771.915995370371</v>
@@ -1612,173 +1583,158 @@
         <v>5.2965699881723696</v>
       </c>
       <c r="K25" s="3">
-        <v>1.5859235452473901E-2</v>
-      </c>
-      <c r="L25" s="3">
         <v>6.0239999999999898E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
         <v>67</v>
       </c>
-      <c r="B26" t="s">
+      <c r="E26" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J26" t="s">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" t="s">
+        <v>79</v>
+      </c>
+      <c r="I27" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" t="s">
+        <v>87</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" t="s">
-        <v>72</v>
-      </c>
-      <c r="I26" t="s">
-        <v>73</v>
-      </c>
-      <c r="J26" t="s">
-        <v>74</v>
-      </c>
-      <c r="K26" t="s">
-        <v>73</v>
-      </c>
-      <c r="L26" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="2">
-        <v>45781.983182870368</v>
-      </c>
-      <c r="E27" s="1">
-        <v>7.6052999999999997</v>
-      </c>
-      <c r="F27" s="1">
-        <v>166665402.107407</v>
-      </c>
-      <c r="G27" s="1">
-        <v>371643127.41851801</v>
-      </c>
-      <c r="H27" s="1">
-        <v>541676875.56666601</v>
-      </c>
-      <c r="I27" s="1">
-        <v>1.9182114339743499E-3</v>
-      </c>
-      <c r="J27" s="1">
-        <v>5.3793103448275801</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1.9182114339743499E-3</v>
-      </c>
-      <c r="L27" s="1">
-        <v>4.7530468248877496E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="2">
-        <v>45781.990671296298</v>
-      </c>
-      <c r="E28" s="1">
-        <v>8.3330777777777705</v>
-      </c>
-      <c r="F28" s="1">
-        <v>93093916.759259194</v>
-      </c>
-      <c r="G28" s="1">
-        <v>233512023.80740699</v>
-      </c>
-      <c r="H28" s="1">
-        <v>310325298.04444402</v>
-      </c>
-      <c r="I28" s="1">
-        <v>1.5685901340909299E-3</v>
-      </c>
-      <c r="J28" s="1">
-        <v>4.5517241379310303</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1.5685901340909299E-3</v>
-      </c>
-      <c r="L28" s="1">
-        <v>4.7608200455580797E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
       <c r="D29" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K29" t="s">
-        <v>81</v>
-      </c>
-      <c r="L29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30" s="2">
         <v>45772.371192129627</v>
@@ -1802,21 +1758,18 @@
         <v>4.5517712252195697</v>
       </c>
       <c r="K30" s="1">
-        <v>2.0634828401515102E-3</v>
-      </c>
-      <c r="L30" s="1">
         <v>5.2272727272727202E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:11">
       <c r="A31" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" s="4">
         <v>45772.393078703702</v>
@@ -1840,9 +1793,6 @@
         <v>5.3793103448275801</v>
       </c>
       <c r="K31" s="3">
-        <v>2.7961920628205099E-3</v>
-      </c>
-      <c r="L31" s="3">
         <v>8.4459459459459603E-3</v>
       </c>
     </row>
